--- a/ListBrothersFr.xlsx
+++ b/ListBrothersFr.xlsx
@@ -9,27 +9,31 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="913" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="913" activeTab="4"/>
   </bookViews>
   <sheets>
-    <sheet name="Dossiers des Frères Paternels" sheetId="48" r:id="rId1"/>
-    <sheet name="Dossiers des Frères Maternels" sheetId="47" r:id="rId2"/>
-    <sheet name="Dossiers Unique" sheetId="49" r:id="rId3"/>
+    <sheet name="Dossiers des Frères" sheetId="50" r:id="rId1"/>
+    <sheet name="Dossiers des Frères Paternels" sheetId="48" r:id="rId2"/>
+    <sheet name="Dossiers des Frères Maternels" sheetId="47" r:id="rId3"/>
+    <sheet name="Dossiers Unique" sheetId="49" r:id="rId4"/>
+    <sheet name="Statistiques" sheetId="51" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dossiers des Frères Maternels'!$A$6:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dossiers des Frères Paternels'!$A$6:$J$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dossiers Unique'!$A$6:$I$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Dossiers des Frères Maternels'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dossiers des Frères Paternels'!$A$1:$N$7</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Dossiers Unique'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dossiers des Frères'!$A$6:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Dossiers des Frères Maternels'!$A$6:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Dossiers des Frères Paternels'!$A$6:$J$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Dossiers Unique'!$A$6:$I$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Dossiers des Frères'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Dossiers des Frères Maternels'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Dossiers des Frères Paternels'!$A$1:$N$7</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Dossiers Unique'!$A$1:$N$9</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="18">
   <si>
     <t>Classement</t>
   </si>
@@ -80,6 +84,9 @@
   </si>
   <si>
     <t>Taux de compatibilter</t>
+  </si>
+  <si>
+    <t>Dossiers des Frères</t>
   </si>
 </sst>
 </file>
@@ -390,31 +397,7 @@
     <cellStyle name="Style 2" xfId="2"/>
     <cellStyle name="Style 6" xfId="3"/>
   </cellStyles>
-  <dxfs count="99">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="20"/>
-        <color theme="1" tint="0.249977111117893"/>
-        <name val="Mohammad Bold Normal"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="6" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
-    </dxf>
+  <dxfs count="130">
     <dxf>
       <font>
         <b/>
@@ -462,6 +445,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -494,6 +513,40 @@
         <vertAlign val="baseline"/>
         <sz val="18"/>
         <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -525,6 +578,40 @@
         <vertAlign val="baseline"/>
         <sz val="18"/>
         <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
@@ -561,6 +648,40 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -601,6 +722,42 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
@@ -627,6 +784,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -663,6 +856,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -699,6 +928,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color rgb="FF2525FF"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -735,6 +1000,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color rgb="FF008600"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -771,6 +1072,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color rgb="FF660066"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -808,6 +1145,42 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -844,230 +1217,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="double">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Mohammad Head"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Mohammad Head"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Mohammad Head"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
         <color theme="1"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -1104,42 +1253,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
         <color rgb="FFFF0000"/>
         <name val="Arial"/>
         <scheme val="none"/>
@@ -1150,1179 +1263,9 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF2525FF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF008600"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF660066"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="double">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="double">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="double">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Mohammad Head"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Mohammad Head"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Mohammad Head"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF2525FF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF2525FF"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF008600"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF008600"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF660066"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF660066"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
-        <right style="double">
-          <color indexed="64"/>
-        </right>
-        <top style="double">
-          <color indexed="64"/>
-        </top>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FFFF0000"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="double">
-          <color indexed="64"/>
-        </left>
         <right style="double">
           <color indexed="64"/>
         </right>
@@ -2456,54 +1399,34 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="double">
+        <right style="double">
           <color rgb="FF000000"/>
-        </left>
-        <right style="double">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="double">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="double">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="18"/>
-        <color rgb="FF808080"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="20"/>
         <color theme="1" tint="0.249977111117893"/>
-      </font>
+        <name val="Mohammad Bold Normal"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
     <dxf>
       <font>
@@ -3572,6 +2495,2104 @@
         <sz val="20"/>
         <color theme="1" tint="0.249977111117893"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="double">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="double">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="double">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF808080"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="double">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1" tint="0.249977111117893"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Mohammad Head"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF2525FF"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF008600"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FF660066"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="double">
+          <color indexed="64"/>
+        </left>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color rgb="FFFF0000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+        <top style="double">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="double">
+          <color rgb="FF000000"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="double">
+          <color indexed="64"/>
+        </right>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="double">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="20"/>
+        <color theme="1" tint="0.249977111117893"/>
+        <name val="Mohammad Bold Normal"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="6" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3587,69 +4608,92 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PlusTable234" displayName="PlusTable234" ref="A6:N7" insertRow="1" headerRowDxfId="0" headerRowBorderDxfId="15" tableBorderDxfId="16" totalsRowBorderDxfId="31">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="PlusTable2345" displayName="PlusTable2345" ref="A6:N7" insertRow="1" headerRowDxfId="31" headerRowBorderDxfId="29" tableBorderDxfId="30" totalsRowBorderDxfId="28">
   <autoFilter ref="A6:N7"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="14" totalsRowDxfId="30"/>
-    <tableColumn id="4" name="Nom" dataDxfId="13" totalsRowDxfId="29"/>
-    <tableColumn id="5" name="Prenom" dataDxfId="12" totalsRowDxfId="28"/>
-    <tableColumn id="7" name="Date de naissance" dataDxfId="11" totalsRowDxfId="27"/>
-    <tableColumn id="9" name="Commune de naissance" dataDxfId="10" totalsRowDxfId="26"/>
-    <tableColumn id="10" name="Situation familiale" dataDxfId="9" totalsRowDxfId="25"/>
-    <tableColumn id="11" name="Prenom du père" dataDxfId="8" totalsRowDxfId="24"/>
-    <tableColumn id="12" name="Nom de la Mere" dataDxfId="7" totalsRowDxfId="23"/>
-    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="6" totalsRowDxfId="22"/>
-    <tableColumn id="2" name="Date de depos" dataDxfId="5" totalsRowDxfId="21"/>
-    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="4" totalsRowDxfId="20"/>
-    <tableColumn id="8" name="Numero de dossier" dataDxfId="3" totalsRowDxfId="19"/>
-    <tableColumn id="6" name="Remarque" dataDxfId="2" totalsRowDxfId="18"/>
-    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="1" totalsRowDxfId="17"/>
+    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="26" totalsRowDxfId="27"/>
+    <tableColumn id="4" name="Nom" dataDxfId="24" totalsRowDxfId="25"/>
+    <tableColumn id="5" name="Prenom" dataDxfId="22" totalsRowDxfId="23"/>
+    <tableColumn id="7" name="Date de naissance" dataDxfId="20" totalsRowDxfId="21"/>
+    <tableColumn id="9" name="Commune de naissance" dataDxfId="18" totalsRowDxfId="19"/>
+    <tableColumn id="10" name="Situation familiale" dataDxfId="16" totalsRowDxfId="17"/>
+    <tableColumn id="11" name="Prenom du père" dataDxfId="14" totalsRowDxfId="15"/>
+    <tableColumn id="12" name="Nom de la Mere" dataDxfId="12" totalsRowDxfId="13"/>
+    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="10" totalsRowDxfId="11"/>
+    <tableColumn id="2" name="Date de depos" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="6" totalsRowDxfId="7"/>
+    <tableColumn id="8" name="Numero de dossier" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="6" name="Remarque" dataDxfId="2" totalsRowDxfId="3"/>
+    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="0" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PlusTable23" displayName="PlusTable23" ref="A6:N7" insertRow="1" headerRowDxfId="65" dataDxfId="64" headerRowBorderDxfId="62" tableBorderDxfId="63" totalsRowBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="PlusTable234" displayName="PlusTable234" ref="A6:N7" insertRow="1" headerRowDxfId="129" headerRowBorderDxfId="128" tableBorderDxfId="127" totalsRowBorderDxfId="126">
   <autoFilter ref="A6:N7"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="59" totalsRowDxfId="60"/>
-    <tableColumn id="4" name="Nom" dataDxfId="57" totalsRowDxfId="58"/>
-    <tableColumn id="5" name="Prenom" dataDxfId="55" totalsRowDxfId="56"/>
-    <tableColumn id="7" name="Date de naissance" dataDxfId="53" totalsRowDxfId="54"/>
-    <tableColumn id="9" name="Commune de naissance" dataDxfId="51" totalsRowDxfId="52"/>
-    <tableColumn id="10" name="Situation familiale" dataDxfId="49" totalsRowDxfId="50"/>
-    <tableColumn id="11" name="Prenom du père" dataDxfId="47" totalsRowDxfId="48"/>
-    <tableColumn id="12" name="Nom de la Mere" dataDxfId="45" totalsRowDxfId="46"/>
-    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="43" totalsRowDxfId="44"/>
-    <tableColumn id="2" name="Date de depos" dataDxfId="41" totalsRowDxfId="42"/>
-    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="36" totalsRowDxfId="40"/>
-    <tableColumn id="8" name="Numero de dossier" dataDxfId="35" totalsRowDxfId="39"/>
-    <tableColumn id="6" name="Remarque" dataDxfId="34" totalsRowDxfId="38"/>
-    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="33" totalsRowDxfId="37"/>
+    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="125" totalsRowDxfId="124"/>
+    <tableColumn id="4" name="Nom" dataDxfId="123" totalsRowDxfId="122"/>
+    <tableColumn id="5" name="Prenom" dataDxfId="121" totalsRowDxfId="120"/>
+    <tableColumn id="7" name="Date de naissance" dataDxfId="119" totalsRowDxfId="118"/>
+    <tableColumn id="9" name="Commune de naissance" dataDxfId="117" totalsRowDxfId="116"/>
+    <tableColumn id="10" name="Situation familiale" dataDxfId="115" totalsRowDxfId="114"/>
+    <tableColumn id="11" name="Prenom du père" dataDxfId="113" totalsRowDxfId="112"/>
+    <tableColumn id="12" name="Nom de la Mere" dataDxfId="111" totalsRowDxfId="110"/>
+    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="109" totalsRowDxfId="108"/>
+    <tableColumn id="2" name="Date de depos" dataDxfId="107" totalsRowDxfId="106"/>
+    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="105" totalsRowDxfId="104"/>
+    <tableColumn id="8" name="Numero de dossier" dataDxfId="103" totalsRowDxfId="102"/>
+    <tableColumn id="6" name="Remarque" dataDxfId="101" totalsRowDxfId="100"/>
+    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="99" totalsRowDxfId="98"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PlusTable2" displayName="PlusTable2" ref="A6:N7" insertRow="1" headerRowDxfId="98" dataDxfId="96" headerRowBorderDxfId="97" tableBorderDxfId="95" totalsRowBorderDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="PlusTable23" displayName="PlusTable23" ref="A6:N7" insertRow="1" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96" tableBorderDxfId="94" totalsRowBorderDxfId="93">
   <autoFilter ref="A6:N7"/>
   <tableColumns count="14">
-    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="93" totalsRowDxfId="92"/>
-    <tableColumn id="4" name="Nom" dataDxfId="91" totalsRowDxfId="90"/>
-    <tableColumn id="5" name="Prenom" dataDxfId="89" totalsRowDxfId="88"/>
-    <tableColumn id="7" name="Date de naissance" dataDxfId="87" totalsRowDxfId="86"/>
-    <tableColumn id="9" name="Commune de naissance" dataDxfId="85" totalsRowDxfId="84"/>
-    <tableColumn id="10" name="Situation familiale" dataDxfId="83" totalsRowDxfId="82"/>
-    <tableColumn id="11" name="Prenom du père" dataDxfId="81" totalsRowDxfId="80"/>
-    <tableColumn id="12" name="Nom de la Mere" dataDxfId="79" totalsRowDxfId="78"/>
-    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="77" totalsRowDxfId="76"/>
-    <tableColumn id="2" name="Date de depos" dataDxfId="75" totalsRowDxfId="74"/>
-    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="73" totalsRowDxfId="72"/>
-    <tableColumn id="8" name="Numero de dossier" dataDxfId="71" totalsRowDxfId="70"/>
-    <tableColumn id="6" name="Remarque" dataDxfId="69" totalsRowDxfId="68"/>
-    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="67" totalsRowDxfId="66"/>
+    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="92" totalsRowDxfId="91"/>
+    <tableColumn id="4" name="Nom" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="5" name="Prenom" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="7" name="Date de naissance" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="9" name="Commune de naissance" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="10" name="Situation familiale" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="11" name="Prenom du père" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="12" name="Nom de la Mere" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="2" name="Date de depos" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="8" name="Numero de dossier" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="6" name="Remarque" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="66" totalsRowDxfId="65"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PlusTable2" displayName="PlusTable2" ref="A6:N7" insertRow="1" headerRowDxfId="64" dataDxfId="62" headerRowBorderDxfId="63" tableBorderDxfId="61" totalsRowBorderDxfId="60">
+  <autoFilter ref="A6:N7"/>
+  <tableColumns count="14">
+    <tableColumn id="1" name="Classement" totalsRowLabel="Total" dataDxfId="59" totalsRowDxfId="58"/>
+    <tableColumn id="4" name="Nom" dataDxfId="57" totalsRowDxfId="56"/>
+    <tableColumn id="5" name="Prenom" dataDxfId="55" totalsRowDxfId="54"/>
+    <tableColumn id="7" name="Date de naissance" dataDxfId="53" totalsRowDxfId="52"/>
+    <tableColumn id="9" name="Commune de naissance" dataDxfId="51" totalsRowDxfId="50"/>
+    <tableColumn id="10" name="Situation familiale" dataDxfId="49" totalsRowDxfId="48"/>
+    <tableColumn id="11" name="Prenom du père" dataDxfId="47" totalsRowDxfId="46"/>
+    <tableColumn id="12" name="Nom de la Mere" dataDxfId="45" totalsRowDxfId="44"/>
+    <tableColumn id="13" name="Prenom de la Mere" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="2" name="Date de depos" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="30" name="Photo" totalsRowFunction="count" dataDxfId="39" totalsRowDxfId="38"/>
+    <tableColumn id="8" name="Numero de dossier" dataDxfId="37" totalsRowDxfId="36"/>
+    <tableColumn id="6" name="Remarque" dataDxfId="35" totalsRowDxfId="34"/>
+    <tableColumn id="3" name="Taux de compatibilter" dataDxfId="33" totalsRowDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3942,6 +4986,166 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="14" width="41.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="82.5" customHeight="1">
+      <c r="A1" s="16"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+    </row>
+    <row r="2" spans="1:14" ht="39">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" ht="39">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+    </row>
+    <row r="4" spans="1:14" ht="153.75" customHeight="1">
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
+    </row>
+    <row r="5" spans="1:14" ht="39">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" ht="159" customHeight="1" thickBot="1">
+      <c r="A6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="200.1" customHeight="1" thickTop="1">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="20"/>
+    </row>
+  </sheetData>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.19685039370078741" bottom="0" header="0.19685039370078741" footer="0"/>
+  <pageSetup paperSize="9" scale="19" orientation="landscape" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
@@ -4101,7 +5305,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N7"/>
@@ -4254,7 +5458,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N7"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15"/>
@@ -4407,4 +5611,13 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>